--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-lm-medication-administration.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-lm-medication-administration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="155">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Entrée Traitement</t>
+    <t>Traitement</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -448,10 +448,34 @@
     <t>fr-lm-entry.header.language</t>
   </si>
   <si>
-    <t>fr-lm-medication-administration.dureeTraitement</t>
-  </si>
-  <si>
-    <t>Durée du traitement</t>
+    <t>fr-lm-medication-administration.medication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication
+</t>
+  </si>
+  <si>
+    <t>Médicament</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-administration.occurrence[x]</t>
+  </si>
+  <si>
+    <t>dateTime
+Period</t>
+  </si>
+  <si>
+    <t>date/ durée du traitement</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-administration.reason[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-conditionhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observation</t>
+  </si>
+  <si>
+    <t>Motif du traitement</t>
   </si>
   <si>
     <t>fr-lm-medication-administration.dosage</t>
@@ -464,24 +488,14 @@
     <t>Posologie</t>
   </si>
   <si>
-    <t>fr-lm-medication-administration.medicament</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication
+    <t>fr-lm-medication-administration.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Médicament</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-administration.reason[x]</t>
-  </si>
-  <si>
-    <t>CodeableConcept
-http://hl7.org/cda/stds/core/StructureDefinition/Reference</t>
-  </si>
-  <si>
-    <t>Motif du traitement</t>
+    <t>Note</t>
   </si>
 </sst>
 </file>
@@ -783,7 +797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ23"/>
+  <dimension ref="A1:AJ24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.28125" customWidth="true" bestFit="true"/>
@@ -796,7 +810,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="133.21484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2746,7 +2760,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>79</v>
@@ -2761,13 +2775,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2821,7 +2835,7 @@
         <v>140</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>79</v>
@@ -2835,10 +2849,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2846,7 +2860,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -2861,13 +2875,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2918,10 +2932,10 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -2935,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2946,10 +2960,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>73</v>
@@ -2961,13 +2975,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3018,13 +3032,13 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>73</v>
@@ -3035,10 +3049,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3049,7 +3063,7 @@
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>73</v>
@@ -3061,13 +3075,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3118,18 +3132,118 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>73</v>
       </c>
     </row>
